--- a/data/raw/event2_raw.xlsx
+++ b/data/raw/event2_raw.xlsx
@@ -532,11 +532,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuti Herawati</t>
+          <t>ENDAH NURPITA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -545,22 +545,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JL. Kalibata Tengah XI RT 18/ RW 4, Kalibata </t>
+          <t>JL. KERJA BAKTI NO 17  RT 003 / RW 007
+MAKASAR JAKARTA TIMUR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalibata</t>
+          <t>MAKASAR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>MAKASAR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -570,7 +571,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.7 KM</t>
+          <t>1.6 KM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -590,7 +591,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eti Nurbaiti</t>
+          <t>Robiatul adawiyah</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -603,32 +604,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jl. mandala v no. 07 rt. 3 rw. 3 cililitan</t>
+          <t>Gg.simbang 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>kelurahan Cililitan</t>
+          <t>Kaliabang tengah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>kecamatan Kramat Jati</t>
+          <t>Bekasi utara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.2 KM</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -648,11 +649,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USMUNAH</t>
+          <t>Hartini 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -661,17 +662,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JL Melati Rt.8/Rw.7 </t>
+          <t>Jl. Ciledug Raya No. 78 RT 002/004 Kebayoran Lama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ragunan</t>
+          <t>Kebayoran Lama Utara</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ps Minggu</t>
+          <t>Kebayoran Lama</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -686,7 +687,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12 KM</t>
+          <t>18 KM</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -706,11 +707,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vera Anggraeni</t>
+          <t>Luluk Maesaroh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -719,22 +720,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Komplek kodam rt 003 rw 02 blok k9</t>
+          <t>Jalan Pejaten Raya/ Komp Depdikbud Rt 6/Rw 6 Pejaten Barat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kramat jati</t>
+          <t>Pejaten Barat</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pasar Minggu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -744,7 +745,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>800 M</t>
+          <t>8.6 KM</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -764,45 +765,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Budi Ristanto</t>
+          <t>Syarifah</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>jalan rawa jaya no 34</t>
+          <t>Jl Setia II B Rt. 007 / rw. 004</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pondok kopi</t>
+          <t>Jatiwaringin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>duren sawit</t>
+          <t>Pd Gede</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13,8 KM</t>
+          <t>4.2 KM</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -822,11 +823,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Soleha.n</t>
+          <t>Hety meilati</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -835,17 +836,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jl. Permata no24</t>
+          <t>Jl.Ciliwung No.59</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kelurahan kebon pala</t>
+          <t>Kelurahan Cililitan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -860,7 +861,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.6 KM</t>
+          <t>2.2 KM</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -880,30 +881,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DWI JOKO PURWONO</t>
+          <t>SITI NURHAYATI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jl. Jengki Cipinang Asem No. 9 rt007/0011</t>
+          <t>KOMP Kodam jaya blok E no 5 RT 002 RW 002</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Kramat jati</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -918,7 +919,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>900 M</t>
+          <t>800 M</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -938,11 +939,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Karmini Anubhawa</t>
+          <t>Komariah 6</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -951,22 +952,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gg Astawana RT7/RW5 </t>
+          <t>Jl. Muara Baru No. 9 RT 007/001 Penjaringan Jakut</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Balekambang</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -976,7 +977,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.4 KM</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -986,7 +987,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -996,11 +997,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Elok Lisawaty</t>
+          <t>Afriyati Utami</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1009,22 +1010,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jl. Percetakan Negara IX</t>
+          <t>Jl. Marjuki 8 rt. 09/rw 014</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rawasari</t>
+          <t>Penggilingan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cempaka Putih</t>
+          <t>Cakung</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jakarta Pusat</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1034,7 +1035,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1044,7 +1045,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -1054,11 +1055,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rosmiyanti</t>
+          <t>Juwita Laraswaty</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1067,22 +1068,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rusunawa Pasar Rumput, Setiabudi Jaksel</t>
+          <t>jalan H. Lukman Rt.008/006 No. 67 D</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pasar Manggis</t>
+          <t>Lubang Buaya</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Setiabudi</t>
+          <t>Cipayung</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1092,7 +1093,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12 KM</t>
+          <t>6 KM</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1112,11 +1113,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Winarsih</t>
+          <t>Darwati</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1125,17 +1126,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kp Kramat RT 05/05</t>
+          <t>Jl. Kayu Manis Barat No. 15 RT 019/004 Kayu Manis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelurahan cililitan</t>
+          <t>Kayu Manis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kramatjati</t>
+          <t>Matraman</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1150,7 +1151,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1160,7 +1161,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1170,35 +1171,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puryat i</t>
+          <t>Siti Mardiana</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jl cakrawala</t>
+          <t>Jl. TrikorA II RT.3/RW9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Gedong</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Pasar Rebo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Jaktim</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1208,7 +1209,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>850 M</t>
+          <t>5 KM</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1228,11 +1229,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Siti Mardiana</t>
+          <t>Neneng</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1241,32 +1242,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jl. TrikorA II RT.3/RW9</t>
+          <t>Jl. Marga Jaya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gedong</t>
+          <t>Bekasi Selatan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5 KM</t>
+          <t>19 KM</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1276,7 +1277,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1286,11 +1287,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>zelfi zafira</t>
+          <t>Rosmiyanti</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1299,22 +1300,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>jl. mandala no. 24</t>
+          <t>Rusunawa Pasar Rumput, Setiabudi Jaksel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>kelurahan Cililitan</t>
+          <t>Pasar Manggis</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>kecamatan Kramatjati</t>
+          <t>Setiabudi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kabupaten Dki Jakarta</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1324,7 +1325,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.5 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1334,7 +1335,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1345,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lilis</t>
+          <t>Najwa aulia rahman</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1357,22 +1358,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JL. TEBET TIMUR 11 D NO.27 RT 8/ RW 5</t>
+          <t>jl.olahraga 1 no 41</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TEBET TIMUR</t>
+          <t>kelurahan cililitan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TEBET KOTA</t>
+          <t>kecamatan kramat jati</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1382,7 +1383,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.2 KM</t>
+          <t>2.3 KM</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1402,31 +1403,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Asep Sudjana</t>
+          <t>Shanty Puspa oktavianty</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jl Pisangan lama III no 3 RT03 RW07 Pisangan
-Timur Pulo gadung</t>
+          <t>Jl Kamboja gg Cempaka no 6A RT 10 RW 01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pisangan Timur</t>
+          <t>Kebon pala</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pulo Gadung</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.5 KM</t>
+          <t>400 M</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1461,11 +1461,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indah Juniar</t>
+          <t>Novia Anggraeni 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JL. USAHA CAWANG RT010/011</t>
+          <t>Jl. Boulevard Serpong No. 21 RT 003/001 Serpong</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cawang</t>
+          <t>Serpong</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Serpong</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Tangerang Selatan</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Banten</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.8 KM</t>
+          <t>35 KM</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1519,11 +1519,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dewi Julianti</t>
+          <t>Dian Kusuma Ningrum</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1532,32 +1532,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rusunawa Pengadegan</t>
+          <t>Jalan Inpres Gg. Hj Asmawi No.30 Tugu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pengadegan</t>
+          <t>Cimanggis</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Cimanggis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Depok</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.9 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -1577,11 +1577,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Robiatul adawiyah</t>
+          <t>YUYUN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gg.simbang 1</t>
+          <t>Gg Jayanti RT01/RW02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaliabang tengah</t>
+          <t>Lenteng Agung</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bekasi utara</t>
+          <t>Jagakarsa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26 KM</t>
+          <t>9.8 KM</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Najwa aulia rahman</t>
+          <t>Rini Handayani 4</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1648,22 +1648,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>jl.olahraga 1 no 41</t>
+          <t>Jl. Yos Sudarso No. 55 RT 009/001 Sukapura Cilincing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>kelurahan cililitan</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>kecamatan kramat jati</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.3 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DIAH MuZTINNINGRUM</t>
+          <t>Muchlid Noor</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jl. Cakrawala No. 38</t>
+          <t xml:space="preserve">Gg. H.Saari RT.4/RW.2 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kelurahan Kebonpala</t>
+          <t>Pinang Ranti</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>550 M</t>
+          <t>6.7 KM</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1751,11 +1751,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tri Susilowati</t>
+          <t>Novia Anggraeni 9</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1764,17 +1764,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalan Al-Bashor II No.24 RT5/ RW 3 </t>
+          <t>Jl. Garuda VII Pulo Gebang Permai No. 5 RT 002/003</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dukuh</t>
+          <t>Pulo Gebang</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Cakung</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5.6 KM</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1809,11 +1809,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nunik Damiasih</t>
+          <t>Sumiyati</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1822,32 +1822,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cipinang Asem RT 014/009</t>
+          <t>Perum.bumi Sindang asri no.32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kebon Pala</t>
+          <t>Sindang mulya</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Cibarusah</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.3 KM</t>
+          <t>49 KM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1867,11 +1867,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sadiyah</t>
+          <t>Sumiati 3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1880,22 +1880,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cililitan besar rt 6/rw 14 no 14</t>
+          <t>Jl. Muara Baru No. 9 RT 007/001 Penjaringan Jakut</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>kramatjati</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>84 M</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1925,45 +1925,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Uyi Nanda Prasaja</t>
+          <t>Fitri Yanti 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jl Rs. Polri Rt.12/Rw.4 </t>
+          <t>Jl. Margonda Raya No. 150 RT 005/003 Beji Depok</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Depok</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.2 KM</t>
+          <t>22 KM</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -1983,11 +1983,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Desi Rofiqo Hermawati</t>
+          <t>Lastri</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1996,17 +1996,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jl. Bellyra IV blok O No.  12</t>
+          <t>Jl. Yos Sudarso No. 55 RT 009/001 Sukapura Cilincing</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pegangsaan Dua</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kelapa Gading</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -2041,11 +2041,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sumiyati</t>
+          <t>Wati Susanti 7</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2054,22 +2054,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Perum.bumi Sindang asri no.32</t>
+          <t>Jl. Transyogi Cibubur No. 8 RT 007/002 Cibubur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sindang mulya</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cibarusah</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>49 KM</t>
+          <t>13 KM</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wiwin Oktaviani</t>
+          <t>Nurhayati 9</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2112,22 +2112,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jl. Tebet Barat Dalam VIII A RT3 / RW 5 </t>
+          <t>Jl. Garuda VII Pulo Gebang Permai No. 5 RT 002/003</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tebet Barat</t>
+          <t>Pulo Gebang</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tebet</t>
+          <t>Cakung</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7.2 KM</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jl kp Pulo nrt 6 RW 5 pinang Ranti</t>
+          <t>Ekka JuniHarni Putri</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2170,19 +2170,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jl kerja bakti IV no 13B</t>
+          <t>Jalan Cipinang asem no 2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>Kebon pala</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>Makasar</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Makasar</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Jakarta Timur</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.2 KM</t>
+          <t>1.3 KM</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2215,30 +2215,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Muchlid Noor</t>
+          <t>Siti Rochanah</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gg. H.Saari RT.4/RW.2 </t>
+          <t>Jl Raya Centex, GG Galur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pinang Ranti</t>
+          <t>Ciracas</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Ciracas</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6.7 KM</t>
+          <t>9.3 KM</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Siti Rochanah</t>
+          <t>Nunik Damiasih</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2286,17 +2286,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jl Raya Centex, GG Galur</t>
+          <t>Cipinang Asem RT 014/009</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ciracas</t>
+          <t>Kebon Pala</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ciracas</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>9.3 KM</t>
+          <t>1.3 KM</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2331,30 +2331,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hety meilati</t>
+          <t>Asep Sudjana</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jl.Ciliwung No.59</t>
+          <t>Jl Pisangan lama III no 3 RT03 RW07 Pisangan
+Timur Pulo gadung</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kelurahan Cililitan</t>
+          <t>Pisangan Timur</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pulo Gadung</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2369,7 +2370,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.2 KM</t>
+          <t>9.5 KM</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2389,11 +2390,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ani Lestari</t>
+          <t>Jubaedah Indah</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2402,32 +2403,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jl. Berlian VII Raya Kramat Jati Indah II, RT 006. RW 014</t>
+          <t>Jl. Ps Garudu No.4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jati Kramat</t>
+          <t>Lubang Buaya</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jati asih</t>
+          <t>Cipayung</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>16 KM</t>
+          <t>5.1 KM</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2447,25 +2448,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indah Widyawati</t>
+          <t>Puryat i</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cawang III, Jl. Kol. Dutomo 3 Rt 006/008 No 74</t>
+          <t>Jl cakrawala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kebon Pala</t>
+          <t>Kebon pala</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2475,7 +2476,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jaktim</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2485,7 +2486,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2 KM</t>
+          <t>850 M</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2505,35 +2506,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunarto </t>
+          <t>Sri hartaty</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jalan Nyata Squardon rt15/rw1 makasar</t>
+          <t>Jl Telaga Permata 6 Rt009/001 No. 18A</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Sunter Jaya</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Tanjung Priok</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2543,7 +2544,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>300 M</t>
+          <t>13 KM</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2563,11 +2564,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chairunnisyah Nst</t>
+          <t>Erni Rahayu 5</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2576,32 +2577,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jl. Kayu Manis Barat Gg. K2 No.15 Rt 019/04</t>
+          <t>Jl. Transyogi Cibubur No. 8 RT 007/002 Cibubur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kelurahan Kayu Manis</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>12 KM</t>
+          <t>13 KM</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2621,11 +2622,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Neneng</t>
+          <t>Soraya safitri</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2634,32 +2635,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jl. Marga Jaya</t>
+          <t>Jl Dewi Sartika no 10 rt 005 rw 013</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bekasi Selatan</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>19 KM</t>
+          <t>2 KM</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2669,7 +2670,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -2679,11 +2680,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dahlia Sukowati</t>
+          <t>Wiwin Oktaviani</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2692,22 +2693,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gg Delima RT.2/ RW.3</t>
+          <t xml:space="preserve">Jl. Tebet Barat Dalam VIII A RT3 / RW 5 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ceger</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cipayung</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2717,7 +2718,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>7.8 KM</t>
+          <t>7.2 KM</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2737,30 +2738,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ineke Fransiska fortunata</t>
+          <t>Budi Ristanto</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jl rajawali gang Bhakti no. 36</t>
+          <t>jalan rawa jaya no 34</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Halim perdana kusuma</t>
+          <t>pondok kopi</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>duren sawit</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2775,7 +2776,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.7 KM</t>
+          <t>13,8 KM</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2795,11 +2796,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sri Oktaviyani</t>
+          <t>Ani Lestari</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2808,32 +2809,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jl. Raya Condet, GG H. Mujeni No. 44</t>
+          <t>Jl. Berlian VII Raya Kramat Jati Indah II, RT 006. RW 014</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kelurahan Cililitan</t>
+          <t>Jati Kramat</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Jati asih</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.5 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2853,11 +2854,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OON KARWATI</t>
+          <t>Karmiati 2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2866,32 +2867,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Komplek Kodam jaya</t>
+          <t>Jl. Raya Bekasi Timur No. 33 RT 004/005 Bekasi Jaya</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kramat jati</t>
+          <t>Bekasi Jaya</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Bekasi Timur</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>800 M</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2901,7 +2902,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -2911,11 +2912,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Susanti</t>
+          <t>Berti</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2924,18 +2925,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kebon Pala 1 Gang Masjid Sa'adatul muslimin Rt 02
-Rw 07</t>
+          <t>Gg mangga no 220 RT 003/ RW 005</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halim Perdana Kusumah</t>
+          <t>Utan kayu utara</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Matraman</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>400 M</t>
+          <t>22 KM</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2970,11 +2970,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sri hartaty</t>
+          <t>INDAH PERMATA SARI</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2983,22 +2983,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jl Telaga Permata 6 Rt009/001 No. 18A</t>
+          <t>Jl. JENGKI CIPINANG ASEM no.9</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sunter Jaya</t>
+          <t>Kelurahan kebon pala</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tanjung Priok</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>13 KM</t>
+          <t>1 KM</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Titin Sumarni</t>
+          <t>Indah Juniar</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jl Damai No.30, RT.10/ RW. 3 Batu Ampar</t>
+          <t>JL. USAHA CAWANG RT010/011</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kelurahan Batu Ampar</t>
+          <t>Cawang</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5.3 KM</t>
+          <t>2.8 KM</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kurnia Agustina</t>
+          <t>Winarsih</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jalan jengki Cipinang Asem no 54</t>
+          <t>Kp Kramat RT 05/05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Kelurahan cililitan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kramatjati</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1.1 KM</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3144,11 +3144,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ekka JuniHarni Putri</t>
+          <t>Dewi Kartika Sari</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3157,32 +3157,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jalan Cipinang asem no 2</t>
+          <t>Harvest City Cluster Sakura Blok 22</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Lambangsari</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Tambun Selatan</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.3 KM</t>
+          <t>42 KM</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3202,11 +3202,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rina Marlina</t>
+          <t>Sari Dewi</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3215,17 +3215,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jalan Masjid Al - Amin I No.32, RT 5/ RW 6</t>
+          <t>Jl. Jatinegara Timur No. 7 RT 010/003</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Rawa Bunga</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Jatinegara</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3.1 KM</t>
+          <t>6.5 KM</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3260,11 +3260,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Endang Budiyanti</t>
+          <t>Novia Anggraeni 6</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3273,22 +3273,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jl Puskesmas No.22</t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kebon Pala</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1.1 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -3318,11 +3318,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Priyanti Lestari</t>
+          <t>Julaeha Rahayu</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3331,17 +3331,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JL DUREN SAWIT  TIMUR NO.6</t>
+          <t>Jl. Cakrawala No.34</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DUREN SAWIT</t>
+          <t>Kebon Pala</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DUREN SAWIT</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>11 KM</t>
+          <t>850 M</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -3376,11 +3376,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Anna luciana</t>
+          <t>Yuliana</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3389,42 +3389,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rusunawa penggilingan tower E4</t>
+          <t>Jl. Margonda Raya No. 150 RT 005/003 Beji Depok</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kelurahan Penggilingan</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Kec Cakung</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Depok</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>24 KM</t>
+          <t>22 KM</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Terdaftar</t>
+          <t>Tidak Terdaftar</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -3434,30 +3434,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RAHMAT FAUZI</t>
+          <t>Nur Darsitah</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JL.Jengki Cipinang Asem no.9 Rt.007 Rw.011</t>
+          <t xml:space="preserve">Jl.Raya Bogor Gg HM Sabar No.40 </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Rambutan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Ciracas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1 KM</t>
+          <t>4.2 KM</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3492,11 +3492,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Soraya safitri</t>
+          <t>Yuliana 9</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3505,22 +3505,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jl Dewi Sartika no 10 rt 005 rw 013</t>
+          <t>Jl. Muara Baru No. 9 RT 007/001 Penjaringan Jakut</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2 KM</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -3550,11 +3550,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sitti fauziawati</t>
+          <t>Suswati</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jln olah raga 1 RT 08/05</t>
+          <t>Komp. Kodam Jaya Rt. 006/02 blok T no. 7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kelurahan cililitan</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.5 KM</t>
+          <t>800 M</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Asrifah</t>
+          <t>Tuti Herawati</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3621,23 +3621,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jl raya Condet kp Kramat RT 05 Rw 05 Cililitan
-Kramat jati Jakarta timur</t>
+          <t xml:space="preserve">JL. Kalibata Tengah XI RT 18/ RW 4, Kalibata </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Kalibata</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pancoran</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3647,7 +3646,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>5.3 KM</t>
+          <t>5.7 KM</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3667,11 +3666,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ambar Kriswijayanti</t>
+          <t>Cicih Suryani 2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3680,22 +3679,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jl  Pelajar No. 23</t>
+          <t>Jl. Ciledug Raya No. 78 RT 002/004 Kebayoran Lama</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sukapura</t>
+          <t>Kebayoran Lama Utara</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cilincing</t>
+          <t>Kebayoran Lama</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3705,7 +3704,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>26 KM</t>
+          <t>18 KM</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3715,7 +3714,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -3725,11 +3724,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YUYUN</t>
+          <t>Titin Mulyati</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3738,22 +3737,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gg Jayanti RT01/RW02</t>
+          <t>JL langgar rt.8/rw.10</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lenteng Agung</t>
+          <t>Cawang</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Jagakarsa</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3763,7 +3762,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>9.8 KM</t>
+          <t>3.7 KM</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3783,11 +3782,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shanty Puspa oktavianty</t>
+          <t>Jl kp Pulo nrt 6 RW 5 pinang Ranti</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3796,12 +3795,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jl Kamboja gg Cempaka no 6A RT 10 RW 01</t>
+          <t>Jl kerja bakti IV no 13B</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3821,7 +3820,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>400 M</t>
+          <t>1.2 KM</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3841,11 +3840,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Titin Abdullah</t>
+          <t>OON KARWATI</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3854,22 +3853,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jl Pinang II Rt.4 / Rw. 2</t>
+          <t>Komplek Kodam jaya</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pd Labu</t>
+          <t>Kramat jati</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cilandak</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3879,7 +3878,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>16 KM</t>
+          <t>800 M</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3899,11 +3898,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Warti Ruliana</t>
+          <t>Kurnia Agustina</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3912,7 +3911,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jl jengki Cipinang asem no 45</t>
+          <t>Jalan jengki Cipinang Asem no 54</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3937,7 +3936,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1.4 KM</t>
+          <t>1.1 KM</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3957,11 +3956,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tatik Kusumawati</t>
+          <t>WULAN KINASIH</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3970,17 +3969,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jl. Raya Bogor No.11, km 28 Rt.7/Rw.5 </t>
+          <t>Jl.Cakrawala No.47</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pekayon</t>
+          <t>KebonPala</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3995,7 +3994,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>9.9 KM</t>
+          <t>1 KM</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4005,7 +4004,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4014,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WULAN KINASIH</t>
+          <t>Jumiyati</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4028,22 +4027,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jl.Cakrawala No.47</t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KebonPala</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4053,7 +4052,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4073,35 +4072,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rosita Handayaningsih</t>
+          <t>Uyi Nanda Prasaja</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rusunawa Green Jagakarsa Jl. Margasatwa Raya No. V</t>
+          <t xml:space="preserve">Jl Rs. Polri Rt.12/Rw.4 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jagakarsa</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Jagakarsa</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4111,7 +4110,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>16 KM</t>
+          <t>2.2 KM</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4131,11 +4130,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Malinda</t>
+          <t>Desi Rofiqo Hermawati</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4144,22 +4143,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jl.ciliwung No.59</t>
+          <t>Jl. Bellyra IV blok O No.  12</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Pegangsaan Dua</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Kelapa Gading</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4169,7 +4168,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2.2 KM</t>
+          <t>18 KM</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4189,11 +4188,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Maina Karnita</t>
+          <t>Sadiyah</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4202,17 +4201,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jl. Cililitan Kecil I No. 4B</t>
+          <t>Cililitan besar rt 6/rw 14 no 14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kelurahan Cililitan</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>kramatjati</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4227,7 +4226,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1.7 KM</t>
+          <t>84 M</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4247,11 +4246,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SITI NURHAYATI</t>
+          <t>Siti chairiyah</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4260,17 +4259,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KOMP Kodam jaya blok E no 5 RT 002 RW 002</t>
+          <t>Cipinang asem rt07 re 011</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kramat jati</t>
+          <t>Kebon pala</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Makasat</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4285,7 +4284,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>800 M</t>
+          <t>1.1 KM</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4305,11 +4304,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jubaedah Indah</t>
+          <t>Sri Oktaviyani</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4318,17 +4317,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jl. Ps Garudu No.4</t>
+          <t>Jl. Raya Condet, GG H. Mujeni No. 44</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lubang Buaya</t>
+          <t>Kelurahan Cililitan</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cipayung</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4343,7 +4342,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>5.1 KM</t>
+          <t>4.5 KM</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4363,11 +4362,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Suswati</t>
+          <t>Sumiyati</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4376,22 +4375,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Komp. Kodam Jaya Rt. 006/02 blok T no. 7</t>
+          <t>Jl. Sekolah Duta</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pd. Pinang</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Kebayoran Lama</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4401,7 +4400,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>800 M</t>
+          <t>10 KM</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4421,45 +4420,45 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Titin Mulyati</t>
+          <t>Supriadi</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JL langgar rt.8/rw.10</t>
+          <t>Jl. Transyogi Cibubur No. 8 RT 007/002 Cibubur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cawang</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3.7 KM</t>
+          <t>13 KM</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4469,7 +4468,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -4479,11 +4478,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Afriyati Utami</t>
+          <t>Endang Budiyanti</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4492,17 +4491,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jl. Marjuki 8 rt. 09/rw 014</t>
+          <t>Jl Puskesmas No.22</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Penggilingan</t>
+          <t>Kebon Pala</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cakung</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4517,7 +4516,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>16 KM</t>
+          <t>1.1 KM</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4537,11 +4536,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dian Kusuma Ningrum</t>
+          <t>SUZAN.TRI WAHYUNI</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4550,32 +4549,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jalan Inpres Gg. Hj Asmawi No.30 Tugu</t>
+          <t>GG.H. Kaiman no. 11</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cimanggis</t>
+          <t>RAWA BUNGA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cimanggis</t>
+          <t>JATINEGARA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Depok</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>12 KM</t>
+          <t>8.4 KM</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4595,11 +4594,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Citra Dewi Sofian</t>
+          <t>Marlina</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4608,17 +4607,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jl Cipinang Cempedak III rt.1/rw.3</t>
+          <t>Jl. Kerja Bakti No. 5 RT 001/003 Makasar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cipinang Cempedak</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Jatinegara</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4633,7 +4632,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>5.5 KM</t>
+          <t>400 M</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -4653,11 +4652,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rini pujiastuti</t>
+          <t>Indah Widyawati</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4666,17 +4665,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jln mayjend sutoyo Rt 04 /01</t>
+          <t>Cawang III, Jl. Kol. Dutomo 3 Rt 006/008 No 74</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Kebon Pala</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4691,7 +4690,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2.3 KM</t>
+          <t>2 KM</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4711,11 +4710,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dwi Murniasih</t>
+          <t>Lastri 3</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4724,22 +4723,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jl.Cakrawala No.39 rt.12 rw.01</t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kelurahan Kebonpala</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kabupaten Dki</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4749,7 +4748,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>900 M</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4759,7 +4758,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -4769,11 +4768,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ENDAH NURPITA</t>
+          <t>Sumiarsih 8</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4782,18 +4781,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JL. KERJA BAKTI NO 17  RT 003 / RW 007
-MAKASAR JAKARTA TIMUR</t>
+          <t>Jl. Kayu Manis Barat No. 15 RT 019/004 Kayu Manis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MAKASAR</t>
+          <t>Kayu Manis</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MAKASAR</t>
+          <t>Matraman</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4808,7 +4806,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1.6 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4818,7 +4816,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -4828,11 +4826,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Yanti Nurlela</t>
+          <t>Malinda</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4841,17 +4839,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">JL. Kayu Manis IX RT.006/RW09 </t>
+          <t>Jl.ciliwung No.59</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kayu Manis</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4866,7 +4864,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>9.3 KM</t>
+          <t>2.2 KM</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4886,11 +4884,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Julaeha Rahayu</t>
+          <t>Agusnawati</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4899,17 +4897,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jl. Cakrawala No.34</t>
+          <t>Jl. Ciliwung no. 114 rt 11 rw 06</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kebon Pala</t>
+          <t>Kelurahan Cililitan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4924,7 +4922,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>850 M</t>
+          <t>2.5 KM</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4934,7 +4932,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -4944,11 +4942,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Syarifah</t>
+          <t>Septiani 9</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4957,22 +4955,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jl Setia II B Rt. 007 / rw. 004</t>
+          <t>Jl. Margonda Raya No. 150 RT 005/003 Beji Depok</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jatiwaringin</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pd Gede</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Depok</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4982,7 +4980,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4.2 KM</t>
+          <t>22 KM</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4992,7 +4990,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5002,11 +5000,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SURATMI</t>
+          <t>Asrifah</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5015,18 +5013,18 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PULO GEBANG PERMAI JALAN WATUBELA RT
-013/09 JAKARTA TIMUR 13950</t>
+          <t>Jl raya Condet kp Kramat RT 05 Rw 05 Cililitan
+Kramat jati Jakarta timur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PULO GEBANG</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CAKUNG</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5041,7 +5039,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>21 KM</t>
+          <t>5.3 KM</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5061,11 +5059,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Luluk Maesaroh</t>
+          <t>Soleha.n</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5074,22 +5072,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jalan Pejaten Raya/ Komp Depdikbud Rt 6/Rw 6 Pejaten Barat</t>
+          <t>Jl. Permata no24</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pejaten Barat</t>
+          <t>Kelurahan kebon pala</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pasar Minggu</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5099,7 +5097,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8.6 KM</t>
+          <t>1.6 KM</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5119,30 +5117,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ahmad subana</t>
+          <t>Erna wulandari</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jl. Kalibata Tengah III</t>
+          <t>JL SEKOLAH DUTA I  RT2/RW14</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kalibata</t>
+          <t>PD PINANG</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>KEBAYORAN LAMA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5157,7 +5155,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>5.7 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5167,7 +5165,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5175,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sukiyem</t>
+          <t>Nani Kusumawati 4</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -5190,22 +5188,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jl. Pd baru III No. 68 </t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cijantung</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5215,7 +5213,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>9.4 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5225,7 +5223,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5235,11 +5233,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dewi Kartika Sari</t>
+          <t>Anna luciana</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5248,32 +5246,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Harvest City Cluster Sakura Blok 22</t>
+          <t>Rusunawa penggilingan tower E4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lambangsari</t>
+          <t>Kelurahan Penggilingan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tambun Selatan</t>
+          <t>Kec Cakung</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>42 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5293,11 +5291,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Juwita Laraswaty</t>
+          <t>Chairunnisyah Nst</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5306,17 +5304,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>jalan H. Lukman Rt.008/006 No. 67 D</t>
+          <t>Jl. Kayu Manis Barat Gg. K2 No.15 Rt 019/04</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lubang Buaya</t>
+          <t>Kelurahan Kayu Manis</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cipayung</t>
+          <t>Matraman</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5331,7 +5329,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>6 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5351,11 +5349,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nindra diyanti</t>
+          <t>Sukiyem</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5364,18 +5362,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jl.raya tengah RT 05/09 Kelurahan tengah kecamatan
-Kramat jati Jakarta Timur 13540</t>
+          <t xml:space="preserve">Jl. Pd baru III No. 68 </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kampung Tengah</t>
+          <t>Cijantung</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pasar Rebo</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5390,7 +5387,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4.3 KM</t>
+          <t>9.4 KM</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5410,11 +5407,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agusnawati</t>
+          <t>SURATMI</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5423,17 +5420,18 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jl. Ciliwung no. 114 rt 11 rw 06</t>
+          <t>PULO GEBANG PERMAI JALAN WATUBELA RT
+013/09 JAKARTA TIMUR 13950</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kelurahan Cililitan</t>
+          <t>PULO GEBANG</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>CAKUNG</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5448,7 +5446,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2.5 KM</t>
+          <t>21 KM</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5468,30 +5466,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Berti</t>
+          <t xml:space="preserve">Sunarto </t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gg mangga no 220 RT 003/ RW 005</t>
+          <t>Jalan Nyata Squardon rt15/rw1 makasar</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Utan kayu utara</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5506,7 +5504,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>22 KM</t>
+          <t>300 M</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5526,35 +5524,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>INDAH PERMATA SARI</t>
+          <t>Dedi Mulyadi</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jl. JENGKI CIPINANG ASEM no.9</t>
+          <t>Jl. Yos Sudarso No. 55 RT 009/001 Sukapura Cilincing</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kelurahan kebon pala</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5564,7 +5562,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5574,7 +5572,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5584,11 +5582,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dra.Endaruna</t>
+          <t>Karmini Anubhawa</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5597,18 +5595,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jl Garuda VII  Perumahan Pulo Gebang Permai Blok
-G6 No 5</t>
+          <t xml:space="preserve">Gg Astawana RT7/RW5 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kelurahan Pulo Gebang</t>
+          <t>Balekambang</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cakung</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5623,7 +5620,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>22 KM</t>
+          <t>5.4 KM</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5643,11 +5640,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Derisma wahyuni</t>
+          <t>Titin Sumarni</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5656,17 +5653,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jl. Jengki gg asem rt007 rwb011 no 68</t>
+          <t>Jl Damai No.30, RT.10/ RW. 3 Batu Ampar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kelurahan kebon pala</t>
+          <t>Kelurahan Batu Ampar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5681,7 +5678,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>700 M</t>
+          <t>5.3 KM</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5691,7 +5688,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5701,11 +5698,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nanik Puji Astuti</t>
+          <t>Citra Dewi Sofian</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5714,17 +5711,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dhirgantara II Halim Perdana Kusuma</t>
+          <t>Jl Cipinang Cempedak III rt.1/rw.3</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Halim</t>
+          <t>Cipinang Cempedak</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Jatinegara</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5739,7 +5736,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>6 KM</t>
+          <t>5.5 KM</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5759,11 +5756,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hartingsih</t>
+          <t>Sulastri Mulyani</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5772,12 +5769,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jalan Bunga Belakang 2  Rt.10, RW.9, Palmerah</t>
+          <t>Jl. Kramat Asem RT 11/ RW 5 Utan Kayu</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Palmerah</t>
+          <t>Utan Kayu Selatan</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5797,7 +5794,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>7.9 KM</t>
+          <t>8.6 KM</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5807,7 +5804,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5817,11 +5814,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Yolanda Hutapea</t>
+          <t>Fitri Yanti</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5830,32 +5827,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jl. Salak Raya No.100 RT 001/ RW 002</t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jati Mekar</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Jati Asih</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>14 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5865,7 +5862,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5875,11 +5872,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Eti Sunarsih</t>
+          <t>Nindra diyanti</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5888,17 +5885,18 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jl. H Nair No.83, A RT 010/RW 1. Lubang Buaya</t>
+          <t>Jl.raya tengah RT 05/09 Kelurahan tengah kecamatan
+Kramat jati Jakarta Timur 13540</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lubang Buaya</t>
+          <t>Kampung Tengah</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cipayung</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5913,7 +5911,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>6.2 KM</t>
+          <t>4.3 KM</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5933,11 +5931,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Erna wulandari</t>
+          <t>Aminah 3</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -5946,32 +5944,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>JL SEKOLAH DUTA I  RT2/RW14</t>
+          <t>Jl. Jatiwaringin Raya No. 45 RT 006/003 Jatiwaringin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PD PINANG</t>
+          <t>Jatiwaringin</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>KEBAYORAN LAMA</t>
+          <t>Pondok Gede</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>16 KM</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5981,7 +5979,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -5991,11 +5989,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Siti chairiyah</t>
+          <t>Komariah 8</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6004,32 +6002,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cipinang asem rt07 re 011</t>
+          <t>Jl. Bintara Jaya No. 7 RT 003/002 Bintara Jaya Bekasi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kebon pala</t>
+          <t>Bintara Jaya</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Makasat</t>
+          <t>Bekasi Barat</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1.1 KM</t>
+          <t>13 KM</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6039,7 +6037,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6049,11 +6047,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sumiyati</t>
+          <t>Nanik Puji Astuti</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6062,22 +6060,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jl. Sekolah Duta</t>
+          <t>Dhirgantara II Halim Perdana Kusuma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pd. Pinang</t>
+          <t>Halim</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kebayoran Lama</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6087,7 +6085,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>10 KM</t>
+          <t>6 KM</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6097,7 +6095,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6107,11 +6105,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nur Darsitah</t>
+          <t>Elok Lisawaty</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6120,22 +6118,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jl.Raya Bogor Gg HM Sabar No.40 </t>
+          <t>Jl. Percetakan Negara IX</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rambutan</t>
+          <t>Rawasari</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ciracas</t>
+          <t>Cempaka Putih</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Pusat</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6145,7 +6143,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>4.2 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6155,7 +6153,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6165,11 +6163,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SUZAN.TRI WAHYUNI</t>
+          <t>zelfi zafira</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6178,22 +6176,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GG.H. Kaiman no. 11</t>
+          <t>jl. mandala no. 24</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RAWA BUNGA</t>
+          <t>kelurahan Cililitan</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JATINEGARA</t>
+          <t>kecamatan Kramatjati</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Kabupaten Dki Jakarta</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6203,7 +6201,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8.4 KM</t>
+          <t>2.5 KM</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6223,11 +6221,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sulastri Mulyani</t>
+          <t>Rohimah 5</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6236,22 +6234,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jl. Kramat Asem RT 11/ RW 5 Utan Kayu</t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Utan Kayu Selatan</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6261,7 +6259,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8.6 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6281,11 +6279,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SRI WAHYUNINGSIH</t>
+          <t>Hindun 6</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6294,32 +6292,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jl TANJUNG VII RT 009/ RW 002 AR1 NO.3</t>
+          <t>Jl. Dewi Sartika No. 4 RT 001/002 Ciputat Tangsel</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KRAMATJATI</t>
+          <t>Ciputat</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>KRAMATJATI</t>
+          <t>Ciputat</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Tangerang Selatan</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Banten</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>1.3 KM</t>
+          <t>30 KM</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6329,7 +6327,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6339,11 +6337,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rukaiyah</t>
+          <t>Vera Anggraeni</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6352,12 +6350,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jl. Damai No. 63 RT.13/RW.8</t>
+          <t>Komplek kodam rt 003 rw 02 blok k9</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Balekambang</t>
+          <t>Kramat jati</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6377,7 +6375,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2.1 KM</t>
+          <t>800 M</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6397,11 +6395,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Duma Simbolon</t>
+          <t>Dewi Julianti</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6410,22 +6408,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jl. Raya Pemuda No. 91, RT 04/RW 11</t>
+          <t>Rusunawa Pengadegan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pengadegan</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Pancoran</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6435,7 +6433,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2.7 KM</t>
+          <t>5.9 KM</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6445,7 +6443,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6455,11 +6453,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fauziah Nurhayati</t>
+          <t>Ineke Fransiska fortunata</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6468,22 +6466,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jl. Tanjung Barat No. 72 RT 13 RW 01</t>
+          <t>Jl rajawali gang Bhakti no. 36</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Halim perdana kusuma</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6493,7 +6491,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>6.0 KM</t>
+          <t>2.7 KM</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6513,11 +6511,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kasmini</t>
+          <t>Dwi Murniasih</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6526,22 +6524,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jl. Pasar Rebo No. 139 RT 13 RW 12</t>
+          <t>Jl.Cakrawala No.39 rt.12 rw.01</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Kelurahan Kebonpala</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Kabupaten Dki</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6551,7 +6549,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2.5 KM</t>
+          <t>900 M</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6561,7 +6559,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -6571,11 +6569,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Retno Dwi Astuti</t>
+          <t>Nani Kusumawati 7</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6584,22 +6582,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jl. Cilandak No. 114 RT.9/RW.12</t>
+          <t>Jl. Sunter Mas Raya No. 18 RT 003/002 Sunter Jaya</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pasar Manggis</t>
+          <t>Sunter Jaya</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Setiabudi</t>
+          <t>Tanjung Priok</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6609,7 +6607,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8.9 KM</t>
+          <t>19 KM</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6619,7 +6617,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6629,30 +6627,30 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ningsih Saodah</t>
+          <t>DWI JOKO PURWONO</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jl. Dewi Sartika No. 92 RT 04 RW 11</t>
+          <t>Jl. Jengki Cipinang Asem No. 9 rt007/0011</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cibubur</t>
+          <t>Kebon pala</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ciracas</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6667,7 +6665,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8.7 KM</t>
+          <t>900 M</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6677,7 +6675,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6685,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hesti Wulandari</t>
+          <t>Nani Kusumawati</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6700,12 +6698,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jl. Batu Ampar No. 74 RT.7/RW.12</t>
+          <t>Jl. Kamboja No. 12 RT 002/001 Kebon Pala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Halim Perdanakusuma</t>
+          <t>Kebon Pala</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6725,7 +6723,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>320 M</t>
+          <t>600 M</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6745,11 +6743,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mulyani</t>
+          <t>Rohimah</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6758,12 +6756,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Jl. Kalimalang No. 132 RT.4/RW.5</t>
+          <t>Jl. Dewi Sartika No. 8 RT 003/005 Cililitan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cawang</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6783,7 +6781,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1.5 KM</t>
+          <t>2 KM</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6803,11 +6801,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Yati Rosmiati</t>
+          <t>USMUNAH</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6816,22 +6814,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jl. Raya Cipayung No. 140 RT 01 RW 06</t>
+          <t xml:space="preserve">JL Melati Rt.8/Rw.7 </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kampung Melayu</t>
+          <t>Ragunan</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Jatinegara</t>
+          <t>Ps Minggu</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6841,7 +6839,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>4.6 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6851,7 +6849,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -6861,11 +6859,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sri Wahyuni</t>
+          <t>Maina Karnita</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6874,17 +6872,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jl. Penggilingan No. 33 RT 11 RW 08</t>
+          <t>Jl. Cililitan Kecil I No. 4B</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kelurahan Cililitan</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6899,17 +6897,17 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1.1 KM</t>
+          <t>1.7 KM</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Tidak Terdaftar</t>
+          <t>Terdaftar</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -6919,11 +6917,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tri Wahyuningsih</t>
+          <t>Ambar Kriswijayanti</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -6932,22 +6930,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jl. Raya Makasar No. 83, RT.008/RW.001</t>
+          <t>Jl  Pelajar No. 23</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kampung Melayu</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Jatinegara</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6957,7 +6955,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>6.5 KM</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6967,7 +6965,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -6977,11 +6975,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sukarsih</t>
+          <t>Romlah</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -6990,22 +6988,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Jl. Duren Tiga No. 113 RT.15/RW.9</t>
+          <t>Jl. Pekayon Raya No. 34 RT 012/005</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kalibata</t>
+          <t>Pekayon</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Pasar Rebo</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7015,7 +7013,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>5.3 KM</t>
+          <t>5.5 KM</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7035,45 +7033,45 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Yuliani</t>
+          <t>RAHMAT FAUZI</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jl. Raya Kukusan No. 62, RT.001/RW.004</t>
+          <t>JL.Jengki Cipinang Asem no.9 Rt.007 Rw.011</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mekarsari</t>
+          <t>Kebon pala</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cimanggis</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Depok</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>11.7 KM</t>
+          <t>1 KM</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7083,7 +7081,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -7093,11 +7091,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Meyla Septiana</t>
+          <t>Marlina 6</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7106,32 +7104,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jl. Bekasi Raya No. 129, RT.013/RW.003</t>
+          <t>Jl. Margonda Raya No. 150 RT 005/003 Beji Depok</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Halim Perdanakusuma</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Beji</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Depok</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>840 M</t>
+          <t>22 KM</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7151,11 +7149,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Siti Aminah</t>
+          <t>Rina Marlina</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7164,22 +7162,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jl. Kalibata Raya No. 77, RT.008/RW.006</t>
+          <t>Jalan Masjid Al - Amin I No.32, RT 5/ RW 6</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tebet Barat</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tebet</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7189,7 +7187,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>5.5 KM</t>
+          <t>3.1 KM</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7209,11 +7207,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cucu Rohayati</t>
+          <t>Septiani 2</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7222,32 +7220,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jl. Raya Pisangan Lama No. 18, RT 13/RW 05</t>
+          <t>Jl. Boulevard Serpong No. 21 RT 003/001 Serpong</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Balekambang</t>
+          <t>Serpong</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Serpong</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Tangerang Selatan</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Banten</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2.6 KM</t>
+          <t>35 KM</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7257,7 +7255,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -7267,11 +7265,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Titi Rostini</t>
+          <t>Rosita Handayaningsih</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7280,22 +7278,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Jl. Rawamangun Muka No. 8 RT 02 RW 05</t>
+          <t>Rusunawa Green Jagakarsa Jl. Margasatwa Raya No. V</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cijantung</t>
+          <t>Jagakarsa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Jagakarsa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7305,7 +7303,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8.2 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7315,7 +7313,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -7325,11 +7323,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Juwita Sari</t>
+          <t>Eka Fitriani 7</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7338,22 +7336,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jl. Inpres No. 89 RT.12/RW.6</t>
+          <t>Jl. Muara Baru No. 9 RT 007/001 Penjaringan Jakut</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Palmeriam</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7363,12 +7361,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9.4 KM</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Tidak Terdaftar</t>
+          <t>Terdaftar</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7383,35 +7381,35 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Asih Rahayu</t>
+          <t>Ahmad subana</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jl. Ciracas No. 66 RT.1/RW.12</t>
+          <t>Jl. Kalibata Tengah III</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Utan Kayu Utara</t>
+          <t>Kalibata</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Pancoran</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7421,12 +7419,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8.0 KM</t>
+          <t>5.7 KM</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Tidak Terdaftar</t>
+          <t>Terdaftar</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7441,11 +7439,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Endang Purwati</t>
+          <t>Tatik Kusumawati</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7454,17 +7452,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jl. Raya Ciracas No. 94, RT 07/RW 02</t>
+          <t xml:space="preserve">Jl. Raya Bogor No.11, km 28 Rt.7/Rw.5 </t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cipinang Besar Selatan</t>
+          <t>Pekayon</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Pasar Rebo</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7479,7 +7477,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2.0 KM</t>
+          <t>9.9 KM</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7499,11 +7497,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Citra Dewi</t>
+          <t>Yolanda Hutapea</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7512,32 +7510,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jl. Matraman Raya No. 130 RT.5/RW.11</t>
+          <t>Jl. Salak Raya No.100 RT 001/ RW 002</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gedong</t>
+          <t>Jati Mekar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Jati Asih</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>7.9 KM</t>
+          <t>14 KM</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7557,11 +7555,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ai Maryani</t>
+          <t>Susanti</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7570,17 +7568,18 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jl. Ciracas No. 108 RT 11 RW 07</t>
+          <t>Kebon Pala 1 Gang Masjid Sa'adatul muslimin Rt 02
+Rw 07</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Batu Ampar</t>
+          <t>Halim Perdana Kusumah</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7595,7 +7594,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2.2 KM</t>
+          <t>400 M</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7605,7 +7604,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -7615,11 +7614,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Eni Purwanti</t>
+          <t>Warti Ruliana</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7628,17 +7627,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jl. Raya Makasar No. 78 RT.5/RW.4</t>
+          <t>Jl jengki Cipinang asem no 45</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gedong</t>
+          <t>Kebon pala</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7653,7 +7652,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8.5 KM</t>
+          <t>1.4 KM</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7673,7 +7672,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Maemunah</t>
+          <t>Hartingsih</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7686,22 +7685,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jl. Tanjung Barat No. 114 RT.11/RW.4</t>
+          <t>Jalan Bunga Belakang 2  Rt.10, RW.9, Palmerah</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pasar Manggis</t>
+          <t>Palmerah</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Setiabudi</t>
+          <t>Matraman</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7711,7 +7710,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8.8 KM</t>
+          <t>7.9 KM</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7731,11 +7730,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dorma Hutabarat</t>
+          <t>Priyanti Lestari</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7744,22 +7743,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jl. Raya Raya Pasar Minggu No. 22, RT 05/RW 09</t>
+          <t>JL DUREN SAWIT  TIMUR NO.6</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kuningan Timur</t>
+          <t>DUREN SAWIT</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Setiabudi</t>
+          <t>DUREN SAWIT</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7769,7 +7768,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8.6 KM</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7789,11 +7788,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Anita Susanti</t>
+          <t>Derisma wahyuni</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7802,19 +7801,19 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jl. Matraman Raya No. 58 RT 13 RW 04</t>
+          <t>Jl. Jengki gg asem rt007 rwb011 no 68</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
+          <t>Kelurahan kebon pala</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
           <t>Makasar</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Makasar</t>
-        </is>
-      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Jakarta Timur</t>
@@ -7827,7 +7826,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2.0 KM</t>
+          <t>700 M</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7847,11 +7846,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dwi Astuti</t>
+          <t>Sulastri 5</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7860,17 +7859,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Jl. Kalimalang No. 117 RT 07 RW 11</t>
+          <t>Jl. Garuda VII Pulo Gebang Permai No. 5 RT 002/003</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Cipinang Besar Selatan</t>
+          <t>Pulo Gebang</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>Cakung</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7885,7 +7884,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>500 M</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7905,11 +7904,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nenden Suminarsih</t>
+          <t>Nuraini 4</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -7918,22 +7917,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jl. Kalibata Raya No. 2 RT.15/RW.2</t>
+          <t>Jl. Sunter Mas Raya No. 18 RT 003/002 Sunter Jaya</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kalibata</t>
+          <t>Sunter Jaya</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Tanjung Priok</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7943,7 +7942,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>5.9 KM</t>
+          <t>19 KM</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7953,7 +7952,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -7963,11 +7962,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Desi Rahmawati</t>
+          <t>Tri Susilowati</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -7976,7 +7975,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Jl. Batu Ampar No. 13, RT.009/RW.004</t>
+          <t xml:space="preserve">Jalan Al-Bashor II No.24 RT5/ RW 3 </t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8001,7 +8000,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>1.9 KM</t>
+          <t>5.6 KM</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8021,11 +8020,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Putri Rahayu Sari</t>
+          <t>Titin Abdullah</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8034,22 +8033,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Jl. Utan Kayu Raya No. 114 RT.10/RW.12</t>
+          <t>Jl Pinang II Rt.4 / Rw. 2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pulo Gebang</t>
+          <t>Pd Labu</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cakung</t>
+          <t>Cilandak</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8059,7 +8058,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8.2 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8079,30 +8078,30 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Marsiyem</t>
+          <t>Sugiyono</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Jl. Narogong No. 122 RT 08 RW 05</t>
+          <t>Jl. Raya Bekasi Timur No. 33 RT 004/005 Bekasi Jaya</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kranji</t>
+          <t>Bekasi Jaya</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bekasi Barat</t>
+          <t>Bekasi Timur</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8117,7 +8116,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>12.2 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8127,7 +8126,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -8137,11 +8136,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Eva Susanna</t>
+          <t>Wulandari 3</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8150,32 +8149,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Jl. Jatiwaringin No. 62, RT.005/RW.008</t>
+          <t>Jl. Yos Sudarso No. 55 RT 009/001 Sukapura Cilincing</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kranji</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bekasi Barat</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>11.8 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8185,7 +8184,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -8195,11 +8194,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sulastri</t>
+          <t>Dahlia Sukowati</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8208,22 +8207,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Jl. Ampera Raya No. 139 RT 02 RW 03</t>
+          <t>Gg Delima RT.2/ RW.3</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kalibata</t>
+          <t>Ceger</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Cipayung</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8233,7 +8232,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6.0 KM</t>
+          <t>7.8 KM</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8253,11 +8252,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Isti Rahayu</t>
+          <t>Teti Haryati 5</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8266,22 +8265,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Jl. Kalimalang No. 107 RT.7/RW.6</t>
+          <t>Jl. Prof. Soepomo No. 27 RT 006/003 Tebet Barat</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dukuh</t>
+          <t>Tebet Barat</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Tebet</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8291,7 +8290,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>1.8 KM</t>
+          <t>12 KM</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8301,7 +8300,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -8311,11 +8310,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Oktavia Sari</t>
+          <t>Eti Nurbaiti</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8324,17 +8323,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Jl. Halim Perdanakusuma No. 148, RT.007/RW.008</t>
+          <t>jl. mandala v no. 07 rt. 3 rw. 3 cililitan</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ciracas</t>
+          <t>kelurahan Cililitan</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ciracas</t>
+          <t>kecamatan Kramat Jati</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8349,7 +8348,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8.3 KM</t>
+          <t>1.2 KM</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8369,11 +8368,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Neni Kurniasih</t>
+          <t>Sitti fauziawati</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8382,32 +8381,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Jl. Beji Timur No. 138 RT 12 RW 12</t>
+          <t>Jln olah raga 1 RT 08/05</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tugu</t>
+          <t>Kelurahan cililitan</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cimanggis</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Depok</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>12.7 KM</t>
+          <t>2.5 KM</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8427,11 +8426,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Wahyuningsih</t>
+          <t>Sumiati</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8440,22 +8439,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Jl. Raya Pegangsaan No. 87 RT.11/RW.11</t>
+          <t>Jl. Ciledug Raya No. 78 RT 002/004 Kebayoran Lama</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pulo Gebang</t>
+          <t>Kebayoran Lama Utara</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cakung</t>
+          <t>Kebayoran Lama</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8465,12 +8464,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>7.2 KM</t>
+          <t>18 KM</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Tidak Terdaftar</t>
+          <t>Terdaftar</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8485,11 +8484,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rahma Wati</t>
+          <t>Septiani 6</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8498,22 +8497,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jl. Srengseng Sawah No. 137, RT.001/RW.007</t>
+          <t>Jl. Yos Sudarso No. 55 RT 009/001 Sukapura Cilincing</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rawajati</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pancoran</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8523,7 +8522,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>4.9 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8533,7 +8532,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -8543,11 +8542,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Diana Pertiwi</t>
+          <t>SRI WAHYUNINGSIH</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8556,17 +8555,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Jl. Raya Pondok Ranggon No. 13, RT 05/RW 07</t>
+          <t>Jl TANJUNG VII RT 009/ RW 002 AR1 NO.3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kebon Pala</t>
+          <t>KRAMATJATI</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>KRAMATJATI</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8581,7 +8580,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1.5 KM</t>
+          <t>1.3 KM</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8601,11 +8600,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Gita Puspita</t>
+          <t>Yayah Sumiyah 8</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8614,22 +8613,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jl. Raya Raya Pegangsaan No. 72, RT 13/RW 07</t>
+          <t>Jl. Muara Baru No. 9 RT 007/001 Penjaringan Jakut</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Penjaringan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8639,7 +8638,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2.0 KM</t>
+          <t>26 KM</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8649,7 +8648,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -8659,11 +8658,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Purbowati</t>
+          <t>Dra.Endaruna</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -8672,32 +8671,33 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jl. Raya Bekasi No. 90, RT.004/RW.011</t>
+          <t>Jl Garuda VII  Perumahan Pulo Gebang Permai Blok
+G6 No 5</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kranji</t>
+          <t>Kelurahan Pulo Gebang</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bekasi Barat</t>
+          <t>Cakung</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>11.8 KM</t>
+          <t>22 KM</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -8717,11 +8717,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Purwanti</t>
+          <t>Yanti Nurlela</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -8730,22 +8730,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Jl. Rawajati No. 52 RT 14 RW 01</t>
+          <t xml:space="preserve">JL. Kayu Manis IX RT.006/RW09 </t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Karet</t>
+          <t>Kayu Manis</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Setiabudi</t>
+          <t>Matraman</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8.0 KM</t>
+          <t>9.3 KM</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8775,35 +8775,35 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ita Kurniawati</t>
+          <t>Slamet Riyadi</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Perempuan</t>
+          <t>Laki - Laki</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jl. Raya Pasar Rebo No. 120, RT 12/RW 05</t>
+          <t>Jl. Yos Sudarso No. 55 RT 009/001 Sukapura Cilincing</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cawang</t>
+          <t>Sukapura</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Cilincing</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>3.3 KM</t>
+          <t>24 KM</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8833,11 +8833,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nurhayati Wulandari</t>
+          <t>Hayati 8</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -8846,37 +8846,37 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Jl. Raya Condet No. 42, RT.005/RW.002</t>
+          <t>Jl. Raya Bekasi Timur No. 33 RT 004/005 Bekasi Jaya</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cililitan</t>
+          <t>Bekasi Jaya</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Kramat Jati</t>
+          <t>Bekasi Timur</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>1.8 KM</t>
+          <t>16 KM</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Terdaftar</t>
+          <t>Tidak Terdaftar</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -8891,11 +8891,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Supartini</t>
+          <t>DIAH MuZTINNINGRUM</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -8904,32 +8904,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Jl. Beji Timur No. 102, RT.012/RW.004</t>
+          <t>Jl. Cakrawala No. 38</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pasir Gunung Selatan</t>
+          <t>Kelurahan Kebonpala</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cimanggis</t>
+          <t>Makasar</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Depok</t>
+          <t>Jakarta Timur</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>12.4 KM</t>
+          <t>550 M</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Hadir</t>
+          <t>Tidak Hadir</t>
         </is>
       </c>
     </row>
@@ -8949,11 +8949,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Novia Oktaviani</t>
+          <t>Rini pujiastuti</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -8962,17 +8962,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Jl. Matraman Raya No. 31, RT.013/RW.010</t>
+          <t>Jln mayjend sutoyo Rt 04 /01</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Utan Kayu Utara</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Matraman</t>
+          <t>Kramat Jati</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8.8 KM</t>
+          <t>2.3 KM</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Tidak Hadir</t>
+          <t>Hadir</t>
         </is>
       </c>
     </row>
@@ -9007,11 +9007,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Maisarah</t>
+          <t>Komariah 5</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9020,32 +9020,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Jl. Cipinang Besar No. 88 RT.1/RW.7</t>
+          <t>Jl. Jatiwaringin Raya No. 45 RT 006/003 Jatiwaringin</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Cipayung</t>
+          <t>Jatiwaringin</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cipayung</t>
+          <t>Pondok Gede</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Jawa Barat</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>5.4 KM</t>
+          <t>11 KM</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9065,35 +9065,35 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Teguh Santoso</t>
+          <t>Lilis</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Jl. Raya Batu Ampar No. 40, RT 07/RW 03</t>
+          <t>JL. TEBET TIMUR 11 D NO.27 RT 8/ RW 5</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>TEBET TIMUR</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Makasar</t>
+          <t>TEBET KOTA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Jakarta Timur</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2.2 KM</t>
+          <t>8.2 KM</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9123,30 +9123,30 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lukman Hakim</t>
+          <t>Eti Sunarsih</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Jl. Raya Batu Ampar No. 112, RT 14/RW 12</t>
+          <t>Jl. H Nair No.83, A RT 010/RW 1. Lubang Buaya</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Baru</t>
+          <t>Lubang Buaya</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pasar Rebo</t>
+          <t>Cipayung</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>7.0 KM</t>
+          <t>6.2 KM</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Muhamad Ridwan</t>
+          <t>Sulastri</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Laki - Laki</t>
+          <t>Perempuan</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Jl. Pisangan Lama No. 116 RT.4/RW.8</t>
+          <t>Jl. Dewi Sartika No. 8 RT 003/005 Cililitan</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dukuh</t>
+          <t>Cililitan</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>1.9 KM</t>
+          <t>2 KM</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">

--- a/data/raw/event2_raw.xlsx
+++ b/data/raw/event2_raw.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Peserta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,24 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,92 +415,100 @@
   </sheetPr>
   <dimension ref="A1:L153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PESERTA PELATIHAN MAKANAN VIRAL SUSHI &amp; ONIGIRI</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MINGGU, 16 NOVEMBER 2025</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ID ANGGOTA</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Usia</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Jenis Kelamin</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Alamat tempat tinggal</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Desa/Kelurahan</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Kecamatan</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Kabupaten/Kota</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Provinsi</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Jarak</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Status Pendaftaran</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Status Kehadiran</t>
         </is>
@@ -532,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENDAH NURPITA</t>
+          <t>P055</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -591,7 +579,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Robiatul adawiyah</t>
+          <t>P143</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -649,7 +637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hartini 4</t>
+          <t>P072</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -707,7 +695,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luluk Maesaroh</t>
+          <t>P102</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -765,7 +753,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Syarifah</t>
+          <t>P187</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -823,7 +811,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hety meilati</t>
+          <t>P076</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -881,7 +869,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SITI NURHAYATI</t>
+          <t>P158</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -939,7 +927,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Komariah 6</t>
+          <t>P095</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -997,7 +985,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Afriyati Utami</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1055,7 +1043,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Juwita Laraswaty</t>
+          <t>P086</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1113,7 +1101,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Darwati</t>
+          <t>P036</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1171,7 +1159,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Siti Mardiana</t>
+          <t>P106</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1229,7 +1217,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Neneng</t>
+          <t>P122</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1287,7 +1275,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rosmiyanti</t>
+          <t>P149</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1345,7 +1333,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Najwa aulia rahman</t>
+          <t>P116</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1403,7 +1391,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shanty Puspa oktavianty</t>
+          <t>P154</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1461,7 +1449,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Novia Anggraeni 3</t>
+          <t>P124</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1519,7 +1507,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dian Kusuma Ningrum</t>
+          <t>P045</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1577,7 +1565,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YUYUN</t>
+          <t>P216</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1635,7 +1623,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rini Handayani 4</t>
+          <t>P141</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1693,7 +1681,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Muchlid Noor</t>
+          <t>P109</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1751,7 +1739,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Novia Anggraeni 9</t>
+          <t>P119</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1809,7 +1797,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sumiyati</t>
+          <t>P176</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1867,7 +1855,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sumiati 3</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1925,7 +1913,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fitri Yanti 6</t>
+          <t>P066</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1983,7 +1971,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lastri</t>
+          <t>P099</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2041,7 +2029,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wati Susanti 7</t>
+          <t>P090</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2099,7 +2087,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nurhayati 9</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2157,7 +2145,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ekka JuniHarni Putri</t>
+          <t>P052</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2215,7 +2203,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Siti Rochanah</t>
+          <t>P144</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2273,7 +2261,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nunik Damiasih</t>
+          <t>P125</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2331,7 +2319,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Asep Sudjana</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2390,7 +2378,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jubaedah Indah</t>
+          <t>P083</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2448,7 +2436,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Puryat i</t>
+          <t>P134</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2506,7 +2494,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sri hartaty</t>
+          <t>P065</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2564,7 +2552,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Erni Rahayu 5</t>
+          <t>P060</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2622,7 +2610,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Soraya safitri</t>
+          <t>P165</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2680,7 +2668,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wiwin Oktaviani</t>
+          <t>P208</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2738,7 +2726,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Budi Ristanto</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2796,7 +2784,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ani Lestari</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2854,7 +2842,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Karmiati 2</t>
+          <t>P088</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2912,7 +2900,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Berti</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2970,7 +2958,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INDAH PERMATA SARI</t>
+          <t>P098</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3028,7 +3016,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Indah Juniar</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3086,7 +3074,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Winarsih</t>
+          <t>P207</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3144,7 +3132,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dewi Kartika Sari</t>
+          <t>P042</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3202,7 +3190,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sari Dewi</t>
+          <t>P217</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3260,7 +3248,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Novia Anggraeni 6</t>
+          <t>P064</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3318,7 +3306,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Julaeha Rahayu</t>
+          <t>P084</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3376,7 +3364,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Yuliana</t>
+          <t>P215</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3434,7 +3422,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nur Darsitah</t>
+          <t>P126</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3492,7 +3480,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yuliana 9</t>
+          <t>P155</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3550,7 +3538,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Suswati</t>
+          <t>P185</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3608,7 +3596,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tuti Herawati</t>
+          <t>P197</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3666,7 +3654,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cicih Suryani 2</t>
+          <t>P031</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3724,7 +3712,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Titin Mulyati</t>
+          <t>P110</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3782,7 +3770,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jl kp Pulo nrt 6 RW 5 pinang Ranti</t>
+          <t>P139</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3840,7 +3828,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OON KARWATI</t>
+          <t>P130</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3898,7 +3886,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kurnia Agustina</t>
+          <t>P096</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3956,7 +3944,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WULAN KINASIH</t>
+          <t>P093</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4014,7 +4002,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jumiyati</t>
+          <t>P097</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4072,7 +4060,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Uyi Nanda Prasaja</t>
+          <t>P200</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4130,7 +4118,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Desi Rofiqo Hermawati</t>
+          <t>P040</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4188,7 +4176,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sadiyah</t>
+          <t>P152</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4246,7 +4234,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Siti chairiyah</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4304,7 +4292,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sri Oktaviyani</t>
+          <t>P137</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4362,7 +4350,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sumiyati</t>
+          <t>P108</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4420,7 +4408,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supriadi</t>
+          <t>P181</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4478,7 +4466,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Endang Budiyanti</t>
+          <t>P056</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4536,7 +4524,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUZAN.TRI WAHYUNI</t>
+          <t>P186</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4594,7 +4582,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Marlina</t>
+          <t>P107</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4652,7 +4640,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Indah Widyawati</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4710,7 +4698,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lastri 3</t>
+          <t>P175</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4768,7 +4756,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sumiarsih 8</t>
+          <t>P105</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4826,7 +4814,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Malinda</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4884,7 +4872,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agusnawati</t>
+          <t>P092</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4942,7 +4930,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Septiani 9</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -5000,7 +4988,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Asrifah</t>
+          <t>P163</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -5059,7 +5047,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Soleha.n</t>
+          <t>P058</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -5117,7 +5105,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Erna wulandari</t>
+          <t>P117</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -5175,7 +5163,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nani Kusumawati 4</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -5233,7 +5221,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Anna luciana</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5291,7 +5279,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chairunnisyah Nst</t>
+          <t>P171</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -5349,7 +5337,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sukiyem</t>
+          <t>P183</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -5407,7 +5395,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SURATMI</t>
+          <t>P179</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -5466,7 +5454,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunarto </t>
+          <t>P037</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -5524,7 +5512,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dedi Mulyadi</t>
+          <t>P089</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5582,7 +5570,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Karmini Anubhawa</t>
+          <t>P173</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5640,7 +5628,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Titin Sumarni</t>
+          <t>P033</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5698,7 +5686,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Citra Dewi Sofian</t>
+          <t>P172</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5756,7 +5744,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sulastri Mulyani</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5814,7 +5802,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fitri Yanti</t>
+          <t>P123</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5872,7 +5860,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nindra diyanti</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -5931,7 +5919,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aminah 3</t>
+          <t>P151</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5989,7 +5977,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Komariah 8</t>
+          <t>P118</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -6047,7 +6035,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nanik Puji Astuti</t>
+          <t>P054</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -6105,7 +6093,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Elok Lisawaty</t>
+          <t>P220</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6163,7 +6151,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>zelfi zafira</t>
+          <t>P145</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6221,7 +6209,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rohimah 5</t>
+          <t>P077</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6279,7 +6267,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hindun 6</t>
+          <t>P050</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -6337,7 +6325,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vera Anggraeni</t>
+          <t>P082</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6395,7 +6383,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dewi Julianti</t>
+          <t>P081</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6453,7 +6441,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ineke Fransiska fortunata</t>
+          <t>P048</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -6511,7 +6499,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dwi Murniasih</t>
+          <t>P094</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -6569,7 +6557,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nani Kusumawati 7</t>
+          <t>P047</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6627,7 +6615,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DWI JOKO PURWONO</t>
+          <t>P087</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6685,7 +6673,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nani Kusumawati</t>
+          <t>P069</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6743,7 +6731,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rohimah</t>
+          <t>P199</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6801,7 +6789,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>USMUNAH</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6859,7 +6847,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Maina Karnita</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6917,7 +6905,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ambar Kriswijayanti</t>
+          <t>P146</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -6975,7 +6963,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Romlah</t>
+          <t>P136</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -7033,7 +7021,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RAHMAT FAUZI</t>
+          <t>P201</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -7091,7 +7079,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marlina 6</t>
+          <t>P191</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -7149,7 +7137,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rina Marlina</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -7207,7 +7195,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Septiani 2</t>
+          <t>P148</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -7265,7 +7253,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Rosita Handayaningsih</t>
+          <t>P051</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -7323,7 +7311,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Eka Fitriani 7</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -7381,7 +7369,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ahmad subana</t>
+          <t>P129</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -7439,7 +7427,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tatik Kusumawati</t>
+          <t>P214</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -7497,7 +7485,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Yolanda Hutapea</t>
+          <t>P113</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -7555,7 +7543,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Susanti</t>
+          <t>P206</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7614,7 +7602,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Warti Ruliana</t>
+          <t>P071</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -7672,7 +7660,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hartingsih</t>
+          <t>P132</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7730,7 +7718,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Priyanti Lestari</t>
+          <t>P114</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -7788,7 +7776,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Derisma wahyuni</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -7846,7 +7834,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sulastri 5</t>
+          <t>P127</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -7904,7 +7892,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nuraini 4</t>
+          <t>P196</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7962,7 +7950,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tri Susilowati</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -8020,7 +8008,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Titin Abdullah</t>
+          <t>P170</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -8078,7 +8066,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sugiyono</t>
+          <t>P210</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -8136,7 +8124,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Wulandari 3</t>
+          <t>P034</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -8194,7 +8182,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dahlia Sukowati</t>
+          <t>P190</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -8252,7 +8240,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Teti Haryati 5</t>
+          <t>P128</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -8310,7 +8298,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Eti Nurbaiti</t>
+          <t>P063</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -8368,7 +8356,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sitti fauziawati</t>
+          <t>P038</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -8426,7 +8414,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sumiati</t>
+          <t>P021</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -8484,7 +8472,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Septiani 6</t>
+          <t>P188</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -8542,7 +8530,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SRI WAHYUNINGSIH</t>
+          <t>P213</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -8600,7 +8588,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Yayah Sumiyah 8</t>
+          <t>P057</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -8658,7 +8646,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dra.Endaruna</t>
+          <t>P212</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -8717,7 +8705,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Yanti Nurlela</t>
+          <t>P162</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -8775,7 +8763,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Slamet Riyadi</t>
+          <t>P073</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8833,7 +8821,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hayati 8</t>
+          <t>P044</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -8891,7 +8879,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DIAH MuZTINNINGRUM</t>
+          <t>P133</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -8949,7 +8937,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rini pujiastuti</t>
+          <t>P203</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -9007,7 +8995,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Komariah 5</t>
+          <t>P101</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -9065,7 +9053,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lilis</t>
+          <t>P177</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -9123,7 +9111,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Eti Sunarsih</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -9181,7 +9169,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sulastri</t>
+          <t>P121</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -9234,10 +9222,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>